--- a/data/trans_bre/P19C06-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P19C06-Provincia-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 1,13</t>
+          <t>-2,08; 1,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 5,22</t>
+          <t>-0,72; 5,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 0,85</t>
+          <t>-4,68; 1,11</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,32; 0,26</t>
+          <t>-8,18; 0,19</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,12 +685,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-46,41; 647,4</t>
+          <t>-48,0; 624,95</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 116,14</t>
+          <t>-100,0; 170,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -760,27 +760,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 1,57</t>
+          <t>-1,84; 1,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 1,04</t>
+          <t>-1,44; 1,03</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,41</t>
+          <t>0,0; 1,26</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 1,26</t>
+          <t>-0,7; 1,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-77,79; 263,1</t>
+          <t>-73,96; 243,07</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>-88,71; —</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 1,19</t>
+          <t>-1,83; 1,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 4,38</t>
+          <t>-0,36; 4,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 1,06</t>
+          <t>-0,62; 1,08</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 1,51</t>
+          <t>-2,14; 1,38</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-40,08; 925,86</t>
+          <t>-39,26; 886,93</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-81,72; 423,83</t>
+          <t>-80,14; 290,13</t>
         </is>
       </c>
     </row>
@@ -960,27 +960,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 2,65</t>
+          <t>-1,92; 2,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 1,0</t>
+          <t>-3,42; 1,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,59; 3,67</t>
+          <t>0,58; 3,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 1,1</t>
+          <t>-1,64; 1,22</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-78,82; 520,86</t>
+          <t>-79,37; 436,67</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-99,22; 421,8</t>
+          <t>-94,45; 683,83</t>
         </is>
       </c>
     </row>
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,91</t>
+          <t>0,0; 3,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 1,21</t>
+          <t>-3,79; 1,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,57; 4,6</t>
+          <t>0,56; 4,82</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,1</t>
+          <t>0,0; 3,86</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 1,56</t>
+          <t>-0,98; 1,53</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 2,28</t>
+          <t>-1,5; 2,22</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 0,0</t>
+          <t>-4,36; 0,17</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 1,12</t>
+          <t>-2,89; 1,02</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; inf</t>
+          <t>-87,3; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-85,13; 310,39</t>
+          <t>-90,56; 196,68</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 2,37</t>
+          <t>-0,55; 2,49</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,06; 2,45</t>
+          <t>0,06; 2,52</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 2,34</t>
+          <t>-1,11; 2,33</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 2,37</t>
+          <t>-0,4; 2,57</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-69,07; 537,13</t>
+          <t>-49,5; 797,67</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-34,23; 1204,24</t>
+          <t>-49,02; 1258,39</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-71,21; 488,13</t>
+          <t>-65,62; 611,06</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-25,77; 672,96</t>
+          <t>-26,0; 747,62</t>
         </is>
       </c>
     </row>
@@ -1360,37 +1360,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 0,32</t>
+          <t>-2,21; 0,3</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 0,88</t>
+          <t>-1,06; 0,8</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 1,64</t>
+          <t>-1,7; 1,58</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 0,76</t>
+          <t>-0,5; 0,75</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-91,11; 78,01</t>
+          <t>-91,53; 66,93</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 576,22</t>
+          <t>-90,81; 475,36</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-55,86; 129,39</t>
+          <t>-56,86; 117,06</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 0,55</t>
+          <t>-0,59; 0,52</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 1,01</t>
+          <t>-0,15; 0,99</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 0,76</t>
+          <t>-0,5; 0,77</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 0,71</t>
+          <t>-0,42; 0,69</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-45,7; 69,27</t>
+          <t>-40,74; 67,3</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-13,4; 143,19</t>
+          <t>-15,83; 135,73</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-30,54; 85,9</t>
+          <t>-33,05; 85,14</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-31,39; 116,68</t>
+          <t>-34,22; 124,9</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P19C06-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P19C06-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-1,6</t>
+          <t>-1,02</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-74,48%</t>
+          <t>-67,92%</t>
         </is>
       </c>
     </row>
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 1,56</t>
+          <t>-2,43; 1,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 5,29</t>
+          <t>-0,64; 5,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 1,11</t>
+          <t>-4,55; 0,9</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,18; 0,19</t>
+          <t>-4,85; 0,2</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,12 +685,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-48,0; 624,95</t>
+          <t>-36,94; 617,29</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 170,2</t>
+          <t>-100,0; 128,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,36</t>
+          <t>0,33</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>72,73%</t>
         </is>
       </c>
     </row>
@@ -760,27 +760,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 1,32</t>
+          <t>-1,93; 1,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 1,03</t>
+          <t>-1,51; 1,03</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,26</t>
+          <t>0,0; 1,3</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 1,22</t>
+          <t>-0,63; 1,24</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-73,96; 243,07</t>
+          <t>-80,17; 229,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-88,71; —</t>
+          <t>-96,41; —</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,12</t>
+          <t>0,2</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>16,8%</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 1,24</t>
+          <t>-1,78; 1,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 4,66</t>
+          <t>-0,44; 4,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 1,08</t>
+          <t>-0,62; 1,11</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 1,38</t>
+          <t>-1,63; 1,44</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-39,26; 886,93</t>
+          <t>-40,55; 882,74</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-80,14; 290,13</t>
+          <t>-77,01; 430,52</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0,02</t>
+          <t>0,27</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-2,18%</t>
+          <t>34,4%</t>
         </is>
       </c>
     </row>
@@ -960,27 +960,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 2,49</t>
+          <t>-1,87; 2,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 1,09</t>
+          <t>-3,0; 1,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,58; 3,45</t>
+          <t>0,56; 3,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 1,22</t>
+          <t>-1,19; 1,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-79,37; 436,67</t>
+          <t>-79,96; 424,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-94,45; 683,83</t>
+          <t>-100,0; 1458,89</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,77</t>
+          <t>0,2</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,26</t>
+          <t>0,0; 3,58</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 1,29</t>
+          <t>-3,8; 1,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,56; 4,82</t>
+          <t>0,56; 4,74</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,86</t>
+          <t>0,0; 0,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-0,52</t>
+          <t>-0,5</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-31,0%</t>
+          <t>-30,98%</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 1,53</t>
+          <t>-0,97; 1,54</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 2,22</t>
+          <t>-1,65; 2,2</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 0,17</t>
+          <t>-4,23; 0,21</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 1,02</t>
+          <t>-2,51; 1,01</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-87,3; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-90,56; 196,68</t>
+          <t>-88,21; 170,68</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1,06</t>
+          <t>1,69</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>124,82%</t>
+          <t>224,77%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 2,49</t>
+          <t>-0,44; 2,51</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,06; 2,52</t>
+          <t>0,02; 2,4</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 2,33</t>
+          <t>-0,85; 2,39</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 2,57</t>
+          <t>0,56; 2,82</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-49,5; 797,67</t>
+          <t>-57,6; 735,26</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-49,02; 1258,39</t>
+          <t>-52,48; 1280,46</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-65,62; 611,06</t>
+          <t>-59,22; 718,83</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-26,0; 747,62</t>
+          <t>24,13; 899,87</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0,11</t>
+          <t>-0,01</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>-2,79%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 0,3</t>
+          <t>-2,06; 0,39</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 0,8</t>
+          <t>-1,04; 0,77</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 1,58</t>
+          <t>-1,68; 1,46</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 0,75</t>
+          <t>-0,69; 0,63</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-91,53; 66,93</t>
+          <t>-91,01; 73,59</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-90,81; 475,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-56,86; 117,06</t>
+          <t>-57,14; 105,46</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-90,48; —</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>0,23</t>
+          <t>0,33</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>42,55%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 0,52</t>
+          <t>-0,48; 0,59</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 0,99</t>
+          <t>-0,08; 1,05</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 0,77</t>
+          <t>-0,47; 0,81</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 0,69</t>
+          <t>-0,12; 0,74</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-40,74; 67,3</t>
+          <t>-34,54; 77,61</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-15,83; 135,73</t>
+          <t>-7,82; 147,41</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-33,05; 85,14</t>
+          <t>-31,63; 98,4</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-34,22; 124,9</t>
+          <t>-13,8; 138,69</t>
         </is>
       </c>
     </row>
